--- a/Data/True_data/current_data/equity_statement.xlsx
+++ b/Data/True_data/current_data/equity_statement.xlsx
@@ -471,7 +471,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -491,7 +490,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>255.89</v>
+        <v>184.48</v>
       </c>
     </row>
     <row r="7">
@@ -501,7 +500,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>193.85</v>
+        <v>190.98</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +510,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-23.01</v>
+        <v>-84.64</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +520,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>426.73</v>
+        <v>290.81</v>
       </c>
     </row>
   </sheetData>
